--- a/modules/30_q2/figures/editable/origin_templates/data_package/13_多初值稳定性散点.xlsx
+++ b/modules/30_q2/figures/editable/origin_templates/data_package/13_多初值稳定性散点.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_多初值稳定性散点" sheetId="1" r:id="R7d79ba259a27463b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_多初值稳定性散点" sheetId="1" r:id="R6dee810dc41045ff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,15 +19,15 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:sz val="10"/>
+      <x:sz val="11"/>
       <x:color rgb="FF222222"/>
-      <x:name val="Microsoft YaHei"/>
+      <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="10"/>
+      <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Microsoft YaHei"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
   <x:fills count="3">
@@ -63,24 +63,18 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -283,192 +277,136 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10.75" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.75" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.75" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="7" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="6" t="str">
         <x:v>10度厚度-X</x:v>
       </x:c>
-      <x:c r="B1" s="7" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>10度RMSE-Y</x:v>
       </x:c>
-      <x:c r="C1" s="7" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>15度厚度-X2</x:v>
       </x:c>
-      <x:c r="D1" s="7" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>15度RMSE-Y2</x:v>
       </x:c>
-      <x:c r="E1" s="7" t="str">
-        <x:v>联合厚度-X3</x:v>
-      </x:c>
-      <x:c r="F1" s="7" t="str">
-        <x:v>联合RMSE-Y3</x:v>
-      </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="8" t="n">
-        <x:v>7.85663582063064</x:v>
-      </x:c>
-      <x:c r="B2" s="8" t="n">
-        <x:v>0.0005982024535347983</x:v>
-      </x:c>
-      <x:c r="C2" s="8" t="n">
-        <x:v>7.622957415207603</x:v>
-      </x:c>
-      <x:c r="D2" s="8" t="n">
-        <x:v>0.0007065215156155058</x:v>
-      </x:c>
-      <x:c r="E2" s="8" t="n">
-        <x:v>7.739015675125983</x:v>
-      </x:c>
-      <x:c r="F2" s="8" t="n">
-        <x:v>0.003948535584038329</x:v>
+      <x:c r="A2" s="2" t="n">
+        <x:v>7.856635820892201</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="n">
+        <x:v>0.0005982024535534</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="n">
+        <x:v>7.622957415197243</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="n">
+        <x:v>0.0007065215156155</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="8" t="n">
-        <x:v>7.131793894365471</x:v>
-      </x:c>
-      <x:c r="B3" s="8" t="n">
-        <x:v>0.0008333862972842569</x:v>
-      </x:c>
-      <x:c r="C3" s="8" t="n">
-        <x:v>6.921774339784884</x:v>
-      </x:c>
-      <x:c r="D3" s="8" t="n">
-        <x:v>0.0007859379737645705</x:v>
-      </x:c>
-      <x:c r="E3" s="8" t="n">
-        <x:v>7.025295850415226</x:v>
-      </x:c>
-      <x:c r="F3" s="8" t="n">
-        <x:v>0.00396641785045404</x:v>
+      <x:c r="A3" s="2" t="n">
+        <x:v>7.131793895597144</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="n">
+        <x:v>0.0008333862972842</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="n">
+        <x:v>6.921774339508455</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="n">
+        <x:v>0.0007859379737645</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="8" t="n">
-        <x:v>7.4949520493397905</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="n">
-        <x:v>0.0014428534604155297</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="n">
-        <x:v>7.270890126261239</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="n">
-        <x:v>0.001716673310680297</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="n">
-        <x:v>7.381984010891651</x:v>
-      </x:c>
-      <x:c r="F4" s="8" t="n">
-        <x:v>0.0041759047864622185</x:v>
+      <x:c r="A4" s="2" t="n">
+        <x:v>7.494952048505562</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="n">
+        <x:v>0.0014428534604155</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="n">
+        <x:v>7.270890126230355</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="n">
+        <x:v>0.0017166733106802</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="8" t="n">
-        <x:v>8.17287261720875</x:v>
-      </x:c>
-      <x:c r="B5" s="8" t="n">
-        <x:v>0.0017791801954637927</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="n">
-        <x:v>8.33577091715674</x:v>
-      </x:c>
-      <x:c r="D5" s="8" t="n">
-        <x:v>0.0017297615720802638</x:v>
-      </x:c>
-      <x:c r="E5" s="8" t="n">
-        <x:v>8.466935048729805</x:v>
-      </x:c>
-      <x:c r="F5" s="8" t="n">
-        <x:v>0.004252579866502744</x:v>
+      <x:c r="A5" s="2" t="n">
+        <x:v>8.172872617337639</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="n">
+        <x:v>0.0017791801954682</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="n">
+        <x:v>8.335770906678725</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="n">
+        <x:v>0.0017297615720802</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="8" t="n">
-        <x:v>6.813385574287125</x:v>
-      </x:c>
-      <x:c r="B6" s="8" t="n">
-        <x:v>0.002017629520474451</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="n">
-        <x:v>7.946856523176485</x:v>
-      </x:c>
-      <x:c r="D6" s="8" t="n">
-        <x:v>0.001866244754092651</x:v>
-      </x:c>
-      <x:c r="E6" s="8" t="n">
-        <x:v>8.056850957865068</x:v>
-      </x:c>
-      <x:c r="F6" s="8" t="n">
-        <x:v>0.004267638518135728</x:v>
+      <x:c r="A6" s="2" t="n">
+        <x:v>6.813385574252154</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="n">
+        <x:v>0.0020176295204744</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="n">
+        <x:v>7.946856521931621</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="n">
+        <x:v>0.0018662447540886</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="8" t="n">
+      <x:c r="A7" s="2" t="n">
         <x:v>8.499999999999998</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="n">
-        <x:v>0.002342869613898707</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="n">
-        <x:v>6.595343311835489</x:v>
-      </x:c>
-      <x:c r="D7" s="8" t="n">
-        <x:v>0.002097047156743863</x:v>
-      </x:c>
-      <x:c r="E7" s="8" t="n">
-        <x:v>6.700345220417981</x:v>
-      </x:c>
-      <x:c r="F7" s="8" t="n">
-        <x:v>0.004349993348564853</x:v>
+      <x:c r="B7" s="2" t="n">
+        <x:v>0.0023428696138985</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="n">
+        <x:v>6.595343308314032</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="n">
+        <x:v>0.0020970471567438</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="8" t="n">
+      <x:c r="A8" s="2" t="n">
         <x:v>6.500000000000001</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="n">
-        <x:v>0.0025972705925964585</x:v>
-      </x:c>
-      <x:c r="C8" s="8" t="n">
-        <x:v>7.2721422820496</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="n">
-        <x:v>0.08659080340972923</x:v>
-      </x:c>
-      <x:c r="E8" s="8" t="n">
-        <x:v>7.251300147864533</x:v>
-      </x:c>
-      <x:c r="F8" s="8" t="n">
-        <x:v>0.08510182044749985</x:v>
+      <x:c r="B8" s="2" t="n">
+        <x:v>0.0025972705925964</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="n">
+        <x:v>7.272142282060386</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="n">
+        <x:v>0.08659080340973</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="8" t="n">
-        <x:v>7.238089745205235</x:v>
-      </x:c>
-      <x:c r="B9" s="8" t="n">
-        <x:v>0.08314060276145063</x:v>
-      </x:c>
-      <x:c r="C9" s="8" t="n">
-        <x:v>8.222248353548244</x:v>
-      </x:c>
-      <x:c r="D9" s="8" t="n">
-        <x:v>0.08914125918549179</x:v>
-      </x:c>
-      <x:c r="E9" s="8" t="n">
-        <x:v>8.194612902287373</x:v>
-      </x:c>
-      <x:c r="F9" s="8" t="n">
-        <x:v>0.08815920071679838</x:v>
+      <x:c r="A9" s="2" t="n">
+        <x:v>7.23808974507857</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="n">
+        <x:v>0.0831406027614508</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="n">
+        <x:v>8.222248479370588</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="n">
+        <x:v>0.0891412591854563</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
